--- a/backend/data/02_FINANCEIRO.xlsx
+++ b/backend/data/02_FINANCEIRO.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="176">
   <si>
     <t>ID_LANCAMENTO</t>
   </si>
@@ -443,6 +443,84 @@
   </si>
   <si>
     <t>SER_000051</t>
+  </si>
+  <si>
+    <t>TPR_000052</t>
+  </si>
+  <si>
+    <t>SER_000052</t>
+  </si>
+  <si>
+    <t>TPR_000053</t>
+  </si>
+  <si>
+    <t>SER_000053</t>
+  </si>
+  <si>
+    <t>TPR_000054</t>
+  </si>
+  <si>
+    <t>SER_000054</t>
+  </si>
+  <si>
+    <t>TPR_000055</t>
+  </si>
+  <si>
+    <t>SER_000055</t>
+  </si>
+  <si>
+    <t>TPR_000056</t>
+  </si>
+  <si>
+    <t>SER_000056</t>
+  </si>
+  <si>
+    <t>TPR_000057</t>
+  </si>
+  <si>
+    <t>SER_000057</t>
+  </si>
+  <si>
+    <t>TPR_000058</t>
+  </si>
+  <si>
+    <t>SER_000058</t>
+  </si>
+  <si>
+    <t>TPR_000059</t>
+  </si>
+  <si>
+    <t>SER_000059</t>
+  </si>
+  <si>
+    <t>TPR_000060</t>
+  </si>
+  <si>
+    <t>SER_000060</t>
+  </si>
+  <si>
+    <t>TPR_000061</t>
+  </si>
+  <si>
+    <t>SER_000061</t>
+  </si>
+  <si>
+    <t>TPR_000062</t>
+  </si>
+  <si>
+    <t>SER_000062</t>
+  </si>
+  <si>
+    <t>TPR_000063</t>
+  </si>
+  <si>
+    <t>SER_000063</t>
+  </si>
+  <si>
+    <t>TPR_000064</t>
+  </si>
+  <si>
+    <t>SER_000064</t>
   </si>
   <si>
     <t>ID_PROGRAMA_EXTRA</t>
@@ -905,16 +983,16 @@
   <sheetData>
     <row r="1" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>16</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>38</v>
@@ -925,10 +1003,10 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>144</v>
+        <v>170</v>
       </c>
       <c r="B2" t="s">
-        <v>145</v>
+        <v>171</v>
       </c>
       <c r="C2">
         <v>90</v>
@@ -945,10 +1023,10 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>146</v>
+        <v>172</v>
       </c>
       <c r="B3" t="s">
-        <v>147</v>
+        <v>173</v>
       </c>
       <c r="C3">
         <v>60</v>
@@ -965,10 +1043,10 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>148</v>
+        <v>174</v>
       </c>
       <c r="B4" t="s">
-        <v>149</v>
+        <v>175</v>
       </c>
       <c r="C4">
         <v>40</v>
@@ -1261,7 +1339,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -2616,6 +2694,344 @@
         <v>1</v>
       </c>
     </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>141</v>
+      </c>
+      <c r="B53" t="s">
+        <v>142</v>
+      </c>
+      <c r="C53">
+        <v>1585</v>
+      </c>
+      <c r="D53">
+        <v>290</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+      <c r="F53">
+        <v>350</v>
+      </c>
+      <c r="G53" s="2">
+        <v>46023</v>
+      </c>
+      <c r="H53" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>143</v>
+      </c>
+      <c r="B54" t="s">
+        <v>144</v>
+      </c>
+      <c r="C54">
+        <v>1585</v>
+      </c>
+      <c r="D54">
+        <v>290</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54">
+        <v>350</v>
+      </c>
+      <c r="G54" s="2">
+        <v>46023</v>
+      </c>
+      <c r="H54" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>145</v>
+      </c>
+      <c r="B55" t="s">
+        <v>146</v>
+      </c>
+      <c r="C55">
+        <v>1600</v>
+      </c>
+      <c r="D55">
+        <v>290</v>
+      </c>
+      <c r="E55">
+        <v>480</v>
+      </c>
+      <c r="F55">
+        <v>350</v>
+      </c>
+      <c r="G55" s="2">
+        <v>46023</v>
+      </c>
+      <c r="H55" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>147</v>
+      </c>
+      <c r="B56" t="s">
+        <v>148</v>
+      </c>
+      <c r="C56">
+        <v>1600</v>
+      </c>
+      <c r="D56">
+        <v>290</v>
+      </c>
+      <c r="E56">
+        <v>480</v>
+      </c>
+      <c r="F56">
+        <v>350</v>
+      </c>
+      <c r="G56" s="2">
+        <v>46023</v>
+      </c>
+      <c r="H56" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>149</v>
+      </c>
+      <c r="B57" t="s">
+        <v>150</v>
+      </c>
+      <c r="C57">
+        <v>1650</v>
+      </c>
+      <c r="D57">
+        <v>290</v>
+      </c>
+      <c r="E57">
+        <v>480</v>
+      </c>
+      <c r="F57">
+        <v>350</v>
+      </c>
+      <c r="G57" s="2">
+        <v>46023</v>
+      </c>
+      <c r="H57" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>151</v>
+      </c>
+      <c r="B58" t="s">
+        <v>152</v>
+      </c>
+      <c r="C58">
+        <v>1700</v>
+      </c>
+      <c r="D58">
+        <v>290</v>
+      </c>
+      <c r="E58">
+        <v>480</v>
+      </c>
+      <c r="F58">
+        <v>350</v>
+      </c>
+      <c r="G58" s="2">
+        <v>46023</v>
+      </c>
+      <c r="H58" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>153</v>
+      </c>
+      <c r="B59" t="s">
+        <v>154</v>
+      </c>
+      <c r="C59">
+        <v>1700</v>
+      </c>
+      <c r="D59">
+        <v>290</v>
+      </c>
+      <c r="E59">
+        <v>480</v>
+      </c>
+      <c r="F59">
+        <v>350</v>
+      </c>
+      <c r="G59" s="2">
+        <v>46023</v>
+      </c>
+      <c r="H59" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>155</v>
+      </c>
+      <c r="B60" t="s">
+        <v>156</v>
+      </c>
+      <c r="C60">
+        <v>1700</v>
+      </c>
+      <c r="D60">
+        <v>290</v>
+      </c>
+      <c r="E60">
+        <v>480</v>
+      </c>
+      <c r="F60">
+        <v>350</v>
+      </c>
+      <c r="G60" s="2">
+        <v>46023</v>
+      </c>
+      <c r="H60" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>157</v>
+      </c>
+      <c r="B61" t="s">
+        <v>158</v>
+      </c>
+      <c r="C61">
+        <v>1700</v>
+      </c>
+      <c r="D61">
+        <v>290</v>
+      </c>
+      <c r="E61">
+        <v>480</v>
+      </c>
+      <c r="F61">
+        <v>350</v>
+      </c>
+      <c r="G61" s="2">
+        <v>46023</v>
+      </c>
+      <c r="H61" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>159</v>
+      </c>
+      <c r="B62" t="s">
+        <v>160</v>
+      </c>
+      <c r="C62">
+        <v>1900</v>
+      </c>
+      <c r="D62">
+        <v>310</v>
+      </c>
+      <c r="E62">
+        <v>515</v>
+      </c>
+      <c r="F62">
+        <v>470</v>
+      </c>
+      <c r="G62" s="2">
+        <v>46023</v>
+      </c>
+      <c r="H62" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>161</v>
+      </c>
+      <c r="B63" t="s">
+        <v>162</v>
+      </c>
+      <c r="C63">
+        <v>1900</v>
+      </c>
+      <c r="D63">
+        <v>310</v>
+      </c>
+      <c r="E63">
+        <v>515</v>
+      </c>
+      <c r="F63">
+        <v>470</v>
+      </c>
+      <c r="G63" s="2">
+        <v>46023</v>
+      </c>
+      <c r="H63" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>163</v>
+      </c>
+      <c r="B64" t="s">
+        <v>164</v>
+      </c>
+      <c r="C64">
+        <v>1900</v>
+      </c>
+      <c r="D64">
+        <v>310</v>
+      </c>
+      <c r="E64">
+        <v>515</v>
+      </c>
+      <c r="F64">
+        <v>470</v>
+      </c>
+      <c r="G64" s="2">
+        <v>46023</v>
+      </c>
+      <c r="H64" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>165</v>
+      </c>
+      <c r="B65" t="s">
+        <v>166</v>
+      </c>
+      <c r="C65">
+        <v>1910</v>
+      </c>
+      <c r="D65">
+        <v>330</v>
+      </c>
+      <c r="E65">
+        <v>515</v>
+      </c>
+      <c r="F65">
+        <v>470</v>
+      </c>
+      <c r="G65" s="2">
+        <v>46023</v>
+      </c>
+      <c r="H65" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
